--- a/backend/app/agent_artifacts/templates/kol_selection_v3.xlsx
+++ b/backend/app/agent_artifacts/templates/kol_selection_v3.xlsx
@@ -12,9 +12,7 @@
     <sheet name="粉丝画像详情" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="评分方法论与数据来源" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames>
-    <definedName name="TEMPLATE_VERSION">'达人圈选总表'!$A$1000</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -649,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1000"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -671,18 +669,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>湖州小红书颜值达人 — KOL匹配度筛选分析报告</t>
-        </is>
-      </c>
+      <c r="A1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>客户: 湖州 | 报告日期: 2026-07-09 | 达人总数: 13 | MCP收录: 12 | 未收录: 1</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
@@ -983,18 +973,6 @@
       <c r="C26" s="18" t="n"/>
       <c r="D26" s="18" t="n"/>
       <c r="E26" s="18" t="n"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr">
-        <is>
-          <t>gate-c-v1</t>
-        </is>
-      </c>
-      <c r="B1000" t="inlineStr">
-        <is>
-          <t>template_version</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4687,40 +4665,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>评分方法论与数据来源</t>
-        </is>
-      </c>
-    </row>
+      <c r="A1" s="1" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>一、评分维度与计算方式</t>
-        </is>
-      </c>
+      <c r="A3" s="28" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>满分</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>计算方式</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
